--- a/De-Para_Empresa_0002.xlsx
+++ b/De-Para_Empresa_0002.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="De-Para" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="De-Para" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Conta Débito</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Conta Crédito</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Centro de Custo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Histórico</t>
         </is>
       </c>
     </row>
@@ -439,16 +454,23 @@
           <t>001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -456,16 +478,23 @@
           <t>007</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -473,16 +502,23 @@
           <t>009</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -490,16 +526,23 @@
           <t>015</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -507,16 +550,23 @@
           <t>020</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -524,16 +574,23 @@
           <t>025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -541,16 +598,23 @@
           <t>055</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -558,16 +622,23 @@
           <t>066</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -575,16 +646,23 @@
           <t>067</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -592,16 +670,23 @@
           <t>068</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -609,16 +694,23 @@
           <t>069</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -626,16 +718,23 @@
           <t>071</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -643,16 +742,23 @@
           <t>082</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -660,16 +766,23 @@
           <t>086</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>5110100016</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -677,16 +790,23 @@
           <t>093</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -694,16 +814,23 @@
           <t>100</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -711,16 +838,23 @@
           <t>102</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -728,16 +862,23 @@
           <t>117</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -745,16 +886,23 @@
           <t>126</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -762,16 +910,23 @@
           <t>129</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -779,16 +934,23 @@
           <t>147</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -796,16 +958,23 @@
           <t>200</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
         <is>
           <t>2140100005</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -813,16 +982,23 @@
           <t>230</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -830,16 +1006,23 @@
           <t>400</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -847,16 +1030,23 @@
           <t>406</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>1140100008</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -864,16 +1054,23 @@
           <t>412</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
         <is>
           <t>5110100006</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -881,16 +1078,23 @@
           <t>414</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
         <is>
           <t>5110100006</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -898,16 +1102,23 @@
           <t>420</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -915,16 +1126,23 @@
           <t>445</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -932,16 +1150,23 @@
           <t>446</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -949,16 +1174,23 @@
           <t>447</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -966,16 +1198,23 @@
           <t>449</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
         <is>
           <t>5110100007</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -985,6 +1224,13 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -994,6 +1240,13 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1003,6 +1256,13 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1010,16 +1270,23 @@
           <t>495</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1029,6 +1296,13 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1038,6 +1312,13 @@
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1047,6 +1328,13 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1056,6 +1344,13 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1065,6 +1360,13 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1074,6 +1376,13 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1083,6 +1392,13 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1092,6 +1408,13 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1099,16 +1422,23 @@
           <t>599</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
         <is>
           <t>2140100005</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1116,16 +1446,23 @@
           <t>602</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1133,16 +1470,23 @@
           <t>604</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>5110100015</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1150,16 +1494,23 @@
           <t>605</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>5110100017</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1169,6 +1520,13 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1176,16 +1534,23 @@
           <t>609</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1195,6 +1560,13 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1204,6 +1576,13 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1211,16 +1590,23 @@
           <t>615</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>5110100021</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1230,6 +1616,13 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1237,16 +1630,23 @@
           <t>621</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>5110100016</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1256,6 +1656,13 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1263,16 +1670,23 @@
           <t>625</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>5110100017</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1280,16 +1694,23 @@
           <t>626</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1299,6 +1720,13 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1306,16 +1734,23 @@
           <t>635</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>5110100021</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1323,16 +1758,23 @@
           <t>643</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>2140100013</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1342,6 +1784,13 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1351,6 +1800,13 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1360,6 +1816,13 @@
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1367,16 +1830,23 @@
           <t>692</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>5110100017</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1386,6 +1856,13 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1393,16 +1870,23 @@
           <t>704</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>1140100008</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1410,16 +1894,23 @@
           <t>705</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>1140100008</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1427,16 +1918,23 @@
           <t>708</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1444,16 +1942,23 @@
           <t>709</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>2140100002</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1463,6 +1968,13 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1470,16 +1982,23 @@
           <t>716</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1489,6 +2008,13 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1498,6 +2024,13 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1507,6 +2040,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1514,16 +2054,23 @@
           <t>903</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>2140100005</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1533,6 +2080,13 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1540,16 +2094,23 @@
           <t>914</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>2140100007</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1557,16 +2118,23 @@
           <t>998</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1576,12 +2144,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>INSS S/ PRO LABORE (EMPRESA SÓCIOS)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>5110100013</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>2140100005</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PELO VALOR DE INSS S/ PRO LABORE CONF FOLHA</t>
         </is>
       </c>
     </row>
@@ -1591,16 +2174,23 @@
           <t>GPS_RAT</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
         <is>
           <t>5110100013</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>2140100005</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1608,16 +2198,23 @@
           <t>GPS_TERCEIROS</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
         <is>
           <t>5110100013</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>2140100005</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1625,16 +2222,23 @@
           <t>FGTS</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
         <is>
           <t>5110100014</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>2140100002</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1642,16 +2246,23 @@
           <t>109</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1659,16 +2270,23 @@
           <t>113</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1676,16 +2294,23 @@
           <t>128</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
         <is>
           <t>5110100016</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1693,16 +2318,23 @@
           <t>603</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>2140100013</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1710,16 +2342,23 @@
           <t>689</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>5110100021</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1729,12 +2368,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5110100001</t>
+          <t>PRO LABORE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2140100010</t>
+          <t>5110100002</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2140100009</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>PELO VALOR DE PRO LABORE CONF FOLHA</t>
         </is>
       </c>
     </row>
@@ -1746,12 +2400,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2140100010</t>
+          <t>INSS S/ PRO LABORE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
+          <t>2140100009</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>2140100005</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>PELO VALOR DE INSS S/ PRO LABORE CONF FOLHA</t>
         </is>
       </c>
     </row>
@@ -1763,12 +2432,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2140100010</t>
+          <t>IRRF S/ PRO LABORE</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2140100008</t>
+          <t>2140100009</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2140100007</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>PELO VALOR DE IRRF S/ PRO LABORE CONF FOLHA</t>
         </is>
       </c>
     </row>
@@ -1780,6 +2464,13 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1787,16 +2478,23 @@
           <t>032</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1804,16 +2502,23 @@
           <t>033</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1823,6 +2528,13 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1832,6 +2544,13 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1839,16 +2558,23 @@
           <t>107</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>5110100001</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+          <t>5110100001</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1858,6 +2584,13 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1867,6 +2600,13 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1874,16 +2614,23 @@
           <t>637</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2140100001</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
+          <t>2140100001</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>5110100015</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1893,6 +2640,13 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1902,6 +2656,13 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1911,6 +2672,13 @@
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1920,6 +2688,13 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1929,6 +2704,13 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1938,6 +2720,13 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1947,6 +2736,13 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2DIR</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
